--- a/home_inspector_forms/002_furniture_inspection_form--home_inspector_forms.xlsx
+++ b/home_inspector_forms/002_furniture_inspection_form--home_inspector_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seller information</t>
+          <t>Seller Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Type of furniture</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>price_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Price and Date Received</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date_inspected</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Date inspected</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>inspector_info</t>
+          <t>date_inspected</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inspector information</t>
+          <t>Date Inspected</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>time_inspected</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Time Inspected</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>other_info</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Other Information</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>date_received</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Date Received</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other_info</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other information</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>date_received</t>
+          <t>none_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Date received</t>
+          <t>None 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>none_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Contact information</t>
+          <t>None 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,34 +965,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>type_choices</t>
+          <t>material_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Wood</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>type_choices</t>
+          <t>material_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fabric</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fabric</t>
         </is>
       </c>
     </row>
@@ -1182,19 +1021,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>description_choices</t>
+          <t>none_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>description_choices</t>
+          <t>none_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>signature_choices</t>
+          <t>none_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>signature_choices</t>
+          <t>none_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,74 +1093,6 @@
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>none_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>none_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>none_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>none_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
